--- a/Backend/Ebio Backend/Inheritance-Calculation.xlsx
+++ b/Backend/Ebio Backend/Inheritance-Calculation.xlsx
@@ -123,19 +123,19 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -481,13 +481,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col width="28" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20" customWidth="1" style="2" min="2" max="2"/>
+    <col width="26" customWidth="1" style="2" min="1" max="1"/>
+    <col width="16" customWidth="1" style="2" min="2" max="2"/>
     <col width="16" customWidth="1" style="2" min="3" max="16384"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
@@ -501,7 +501,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>23-03-2025</t>
+          <t>13-05-2025</t>
         </is>
       </c>
     </row>
@@ -552,355 +552,135 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>100000000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Funeral &amp; Burial Expenses</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Haq Mehr</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Distributable Amount</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Debt &amp; Loans</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>5000000</v>
-      </c>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Heir Details</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Will</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>30000000</v>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Heir Relation</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Heir Category</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Shares Amount</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Share For Each Person</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Share Amount For Each Person</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Distributable Amount</t>
-        </is>
-      </c>
-      <c r="B12" s="11">
-        <f>B7 - SUM(B8:B11)</f>
+      <c r="A12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Daughter</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="E12" s="13">
+        <f>D12*B8</f>
         <v/>
       </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Heir Details</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Heir Relation</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Heir Category</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Shares</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Shares Amount</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Share For Each Person</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Share Amount For Each Person</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="F12" s="12">
+        <f>D12/A12</f>
+        <v/>
+      </c>
+      <c r="G12" s="13">
+        <f>F12*B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Son</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Children</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
-        <v>0.4557291666666667</v>
-      </c>
-      <c r="E16" s="9">
-        <f>D16*B12</f>
+      <c r="D13" s="12" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="E13" s="13">
+        <f>D13*B8</f>
         <v/>
       </c>
-      <c r="F16" s="13">
-        <f>D16/A16</f>
+      <c r="F13" s="12">
+        <f>D13/A13</f>
         <v/>
       </c>
-      <c r="G16" s="9">
-        <f>F16*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Children</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>0.1519097222222222</v>
-      </c>
-      <c r="E17" s="9">
-        <f>D17*B12</f>
-        <v/>
-      </c>
-      <c r="F17" s="13">
-        <f>D17/A17</f>
-        <v/>
-      </c>
-      <c r="G17" s="9">
-        <f>F17*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>0.1458333333333333</v>
-      </c>
-      <c r="E18" s="9">
-        <f>D18*B12</f>
-        <v/>
-      </c>
-      <c r="F18" s="13">
-        <f>D18/A18</f>
-        <v/>
-      </c>
-      <c r="G18" s="9">
-        <f>F18*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>0.1215277777777778</v>
-      </c>
-      <c r="E19" s="9">
-        <f>D19*B12</f>
-        <v/>
-      </c>
-      <c r="F19" s="13">
-        <f>D19/A19</f>
-        <v/>
-      </c>
-      <c r="G19" s="9">
-        <f>F19*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Spouse</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E20" s="9">
-        <f>D20*B12</f>
-        <v/>
-      </c>
-      <c r="F20" s="13">
-        <f>D20/A20</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>F20*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Real Brother</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Sibling</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9">
-        <f>D21*B12</f>
-        <v/>
-      </c>
-      <c r="F21" s="13">
-        <f>D21/A21</f>
-        <v/>
-      </c>
-      <c r="G21" s="9">
-        <f>F21*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Real Sister</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Sibling</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9">
-        <f>D22*B12</f>
-        <v/>
-      </c>
-      <c r="F22" s="13">
-        <f>D22/A22</f>
-        <v/>
-      </c>
-      <c r="G22" s="9">
-        <f>F22*B12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Father's Mother</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9">
-        <f>D23*B12</f>
-        <v/>
-      </c>
-      <c r="F23" s="13">
-        <f>D23/A23</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>F23*B12</f>
+      <c r="G13" s="13">
+        <f>F13*B8</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
